--- a/Assets/_OriginalData/Excel/Config/Common/Page.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/Page.xlsx
@@ -391,24 +391,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color indexed="0"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,12 +418,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.05"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,7 +738,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -768,16 +762,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -786,89 +780,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -880,8 +874,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1456,7 +1451,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -1477,7 +1472,7 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -1578,7 +1573,7 @@
       <c r="A18" s="6">
         <v>12</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="5">
@@ -1599,7 +1594,7 @@
       <c r="A19" s="6">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="5">
@@ -1620,7 +1615,7 @@
       <c r="A20" s="6">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C20" s="5">
@@ -1641,7 +1636,7 @@
       <c r="A21" s="6">
         <v>15</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C21" s="5">
@@ -1662,7 +1657,7 @@
       <c r="A22" s="6">
         <v>16</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="5">
@@ -1683,7 +1678,7 @@
       <c r="A23" s="6">
         <v>17</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="5">
@@ -1704,7 +1699,7 @@
       <c r="A24" s="6">
         <v>18</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="6">
@@ -1725,7 +1720,7 @@
       <c r="A25" s="6">
         <v>19</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="6">
@@ -1740,28 +1735,28 @@
       <c r="F25" s="6">
         <v>-1</v>
       </c>
-      <c r="G25" s="9"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="16.5" spans="1:7">
       <c r="A26" s="6">
         <v>20</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="9">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9"/>
+      <c r="C26" s="10">
+        <v>1</v>
+      </c>
+      <c r="D26" s="10">
+        <v>1</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:7">
       <c r="A27" s="6">

--- a/Assets/_OriginalData/Excel/Config/Common/Page.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/Page.xlsx
@@ -1472,7 +1472,7 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>

--- a/Assets/_OriginalData/Excel/Config/Common/Page.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/Page.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="500"/>
+    <workbookView windowWidth="22800" windowHeight="11265" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>界面ID</t>
   </si>
@@ -195,28 +195,16 @@
     <t>Guide/MiniGuidePage</t>
   </si>
   <si>
+    <t>Event/TowerMapPage</t>
+  </si>
+  <si>
+    <t>Event/TowerRulePage</t>
+  </si>
+  <si>
     <t>Game/GamePage</t>
   </si>
   <si>
     <t>Game/OverPage</t>
-  </si>
-  <si>
-    <t>MiniGame/MiniMapPage</t>
-  </si>
-  <si>
-    <t>MiniGame/MiniRulePage</t>
-  </si>
-  <si>
-    <t>MiniGame/MiniGameOverPage</t>
-  </si>
-  <si>
-    <t>MiniGame/MiniRevivePopup</t>
-  </si>
-  <si>
-    <t>MiniGame/TowerMapPage</t>
-  </si>
-  <si>
-    <t>MiniGame/TowerRulePage</t>
   </si>
   <si>
     <t>GMPage</t>
@@ -232,7 +220,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +229,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -732,137 +727,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -876,8 +871,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1226,7 +1223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7.44166666666667" customWidth="1"/>
@@ -1720,7 +1717,7 @@
       <c r="A25" s="6">
         <v>19</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="6">
@@ -1735,196 +1732,112 @@
       <c r="F25" s="6">
         <v>-1</v>
       </c>
-      <c r="G25" s="10"/>
+      <c r="G25" s="9"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="16.5" spans="1:7">
       <c r="A26" s="6">
         <v>20</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="10">
-        <v>1</v>
-      </c>
-      <c r="D26" s="10">
-        <v>1</v>
-      </c>
-      <c r="E26" s="10">
-        <v>1</v>
-      </c>
-      <c r="F26" s="10">
-        <v>0</v>
-      </c>
-      <c r="G26" s="10"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:7">
+      <c r="C26" s="5">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="16.5" spans="1:7">
       <c r="A27" s="6">
         <v>21</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="6">
-        <v>0</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="16.5" spans="1:7">
+      <c r="A28" s="11">
+        <v>22</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="12">
+        <v>1</v>
+      </c>
+      <c r="D28" s="12">
+        <v>1</v>
+      </c>
+      <c r="E28" s="12">
+        <v>1</v>
+      </c>
+      <c r="F28" s="12">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:7">
+      <c r="A29" s="11">
+        <v>23</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="11">
+        <v>0</v>
+      </c>
+      <c r="D29" s="11">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11">
         <v>0.8</v>
       </c>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:7">
-      <c r="A28" s="6">
-        <v>22</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="5">
-        <v>1</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:7">
-      <c r="A29" s="6">
-        <v>23</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="5">
-        <v>0</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="G29" s="5"/>
+      <c r="G29" s="6"/>
     </row>
     <row r="30" ht="16.5" spans="1:7">
-      <c r="A30" s="6">
-        <v>24</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="5">
+        <v>99</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5">
         <v>1</v>
       </c>
       <c r="D30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G30" s="5"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:7">
-      <c r="A31" s="6">
-        <v>25</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="5">
-        <v>0</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:7">
-      <c r="A32" s="6">
-        <v>26</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="5">
-        <v>0</v>
-      </c>
-      <c r="D32" s="5">
-        <v>0</v>
-      </c>
-      <c r="E32" s="5">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:7">
-      <c r="A33" s="6">
-        <v>27</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="5">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:7">
-      <c r="A34" s="5">
-        <v>99</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="G34" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
